--- a/data/SAM-1000L-B7H4-experiment/SAM-1000L-B7H4-MasterDataTable.xlsx
+++ b/data/SAM-1000L-B7H4-experiment/SAM-1000L-B7H4-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mydrive.gsk.com/personal/zach_a_hatzenbeller_gsk_com/Documents/Documents/GitHub/state-space-model/data/SAM-1000L-B7H4-experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="439" documentId="13_ncr:1_{ED1254C4-4D75-4A8F-AEE2-0F1B38868770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25AACBB4-9264-45C9-A175-7A08CCC1FBEC}"/>
+  <xr:revisionPtr revIDLastSave="445" documentId="13_ncr:1_{ED1254C4-4D75-4A8F-AEE2-0F1B38868770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF805EBE-DC93-4DE5-A6BD-6C1175414FE5}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -1818,7 +1818,7 @@
         <v>7.15</v>
       </c>
       <c r="V7" s="1">
-        <v>40.125</v>
+        <v>0</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>6.95</v>
       </c>
       <c r="V8" s="1">
-        <v>40.125</v>
+        <v>40125</v>
       </c>
       <c r="W8">
         <v>0</v>
@@ -1988,7 +1988,7 @@
         <v>6.96</v>
       </c>
       <c r="V9" s="1">
-        <v>80.25</v>
+        <v>40125</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>6.99</v>
       </c>
       <c r="V10" s="1">
-        <v>80.25</v>
+        <v>80250</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         <v>7.07</v>
       </c>
       <c r="V11" s="1">
-        <v>120.375</v>
+        <v>80250</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>7.11</v>
       </c>
       <c r="V12" s="1">
-        <v>120.375</v>
+        <v>120375</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>7.17</v>
       </c>
       <c r="V13" s="1">
-        <v>160.5</v>
+        <v>120375</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>7.16</v>
       </c>
       <c r="V14" s="1">
-        <v>160.5</v>
+        <v>160500</v>
       </c>
       <c r="W14">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         <v>7.13</v>
       </c>
       <c r="V15" s="1">
-        <v>200.625</v>
+        <v>160500</v>
       </c>
       <c r="W15">
         <v>0</v>
@@ -2583,7 +2583,7 @@
         <v>7.07</v>
       </c>
       <c r="V16" s="1">
-        <v>200.625</v>
+        <v>200625</v>
       </c>
       <c r="W16">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>7.03</v>
       </c>
       <c r="V17" s="11">
-        <v>200.625</v>
+        <v>200625</v>
       </c>
       <c r="W17" s="12">
         <v>0</v>
@@ -2764,6 +2764,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -2986,15 +2995,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
@@ -3007,6 +3007,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3025,14 +3033,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{bea66b2b-af80-48b6-873b-d341d3035cfa}" enabled="1" method="Standard" siteId="{63982aff-fb6c-4c22-973b-70e4acfb63e6}" contentBits="0" removed="0"/>
